--- a/AAII_Financials/Quarterly/XITO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/XITO_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="92">
   <si>
     <t>XITO</t>
   </si>
@@ -656,122 +656,125 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AA102"/>
+  <dimension ref="A5:AB102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43738</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43555</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43465</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43373</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43281</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43190</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -847,8 +850,11 @@
       <c r="AA8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -924,8 +930,11 @@
       <c r="AA9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1001,8 +1010,11 @@
       <c r="AA10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1030,8 +1042,9 @@
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
-    </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB11" s="3"/>
+    </row>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1107,8 +1120,11 @@
       <c r="AA12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1184,8 +1200,11 @@
       <c r="AA13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1261,8 +1280,11 @@
       <c r="AA14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1338,8 +1360,11 @@
       <c r="AA15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1364,8 +1389,9 @@
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
-    </row>
-    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB16" s="3"/>
+    </row>
+    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1430,7 +1456,7 @@
         <v>0</v>
       </c>
       <c r="X17" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Y17" s="3">
         <v>100</v>
@@ -1439,10 +1465,13 @@
         <v>100</v>
       </c>
       <c r="AA17" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="AB17" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1507,7 +1536,7 @@
         <v>0</v>
       </c>
       <c r="X18" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="Y18" s="3">
         <v>-100</v>
@@ -1516,10 +1545,13 @@
         <v>-100</v>
       </c>
       <c r="AA18" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
+        <v>-100</v>
+      </c>
+      <c r="AB18" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1547,8 +1579,9 @@
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
-    </row>
-    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB19" s="3"/>
+    </row>
+    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1624,8 +1657,11 @@
       <c r="AA20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1701,8 +1737,11 @@
       <c r="AA21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1730,8 +1769,8 @@
       <c r="K22" s="3">
         <v>0</v>
       </c>
-      <c r="L22" s="3" t="s">
-        <v>4</v>
+      <c r="L22" s="3">
+        <v>0</v>
       </c>
       <c r="M22" s="3" t="s">
         <v>4</v>
@@ -1739,8 +1778,8 @@
       <c r="N22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O22" s="3">
-        <v>0</v>
+      <c r="O22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P22" s="3">
         <v>0</v>
@@ -1748,11 +1787,11 @@
       <c r="Q22" s="3">
         <v>0</v>
       </c>
-      <c r="R22" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S22" s="3">
-        <v>0</v>
+      <c r="R22" s="3">
+        <v>0</v>
+      </c>
+      <c r="S22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="T22" s="3">
         <v>0</v>
@@ -1778,8 +1817,11 @@
       <c r="AA22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1844,7 +1886,7 @@
         <v>0</v>
       </c>
       <c r="X23" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="Y23" s="3">
         <v>-100</v>
@@ -1855,8 +1897,11 @@
       <c r="AA23" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB23" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1926,14 +1971,17 @@
       <c r="Y24" s="3">
         <v>0</v>
       </c>
-      <c r="Z24" s="3" t="s">
-        <v>4</v>
+      <c r="Z24" s="3">
+        <v>0</v>
       </c>
       <c r="AA24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2009,8 +2057,11 @@
       <c r="AA25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -2075,7 +2126,7 @@
         <v>0</v>
       </c>
       <c r="X26" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="Y26" s="3">
         <v>-100</v>
@@ -2086,8 +2137,11 @@
       <c r="AA26" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB26" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -2152,7 +2206,7 @@
         <v>0</v>
       </c>
       <c r="X27" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="Y27" s="3">
         <v>-100</v>
@@ -2163,8 +2217,11 @@
       <c r="AA27" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB27" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2240,8 +2297,11 @@
       <c r="AA28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2317,8 +2377,11 @@
       <c r="AA29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2394,8 +2457,11 @@
       <c r="AA30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2471,8 +2537,11 @@
       <c r="AA31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2548,8 +2617,11 @@
       <c r="AA32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -2614,7 +2686,7 @@
         <v>0</v>
       </c>
       <c r="X33" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="Y33" s="3">
         <v>-100</v>
@@ -2625,8 +2697,11 @@
       <c r="AA33" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB33" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2702,8 +2777,11 @@
       <c r="AA34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -2768,7 +2846,7 @@
         <v>0</v>
       </c>
       <c r="X35" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="Y35" s="3">
         <v>-100</v>
@@ -2779,90 +2857,96 @@
       <c r="AA35" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB35" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43738</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43555</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43465</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43373</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43281</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43190</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2890,8 +2974,9 @@
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
-    </row>
-    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB39" s="3"/>
+    </row>
+    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2919,8 +3004,9 @@
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
-    </row>
-    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB40" s="3"/>
+    </row>
+    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
@@ -2996,8 +3082,11 @@
       <c r="AA41" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB41" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3073,8 +3162,11 @@
       <c r="AA42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3150,8 +3242,11 @@
       <c r="AA43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3227,8 +3322,11 @@
       <c r="AA44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3304,8 +3402,11 @@
       <c r="AA45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -3381,8 +3482,11 @@
       <c r="AA46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3458,8 +3562,11 @@
       <c r="AA47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -3535,8 +3642,11 @@
       <c r="AA48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3612,8 +3722,11 @@
       <c r="AA49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3689,8 +3802,11 @@
       <c r="AA50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3766,8 +3882,11 @@
       <c r="AA51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3843,8 +3962,11 @@
       <c r="AA52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3920,8 +4042,11 @@
       <c r="AA53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
@@ -3997,8 +4122,11 @@
       <c r="AA54" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB54" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4026,8 +4154,9 @@
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
-    </row>
-    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB55" s="3"/>
+    </row>
+    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4055,8 +4184,9 @@
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
-    </row>
-    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB56" s="3"/>
+    </row>
+    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -4132,8 +4262,11 @@
       <c r="AA57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4183,7 +4316,7 @@
         <v>0</v>
       </c>
       <c r="S58" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T58" s="3">
         <v>100</v>
@@ -4209,8 +4342,11 @@
       <c r="AA58" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB58" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -4224,7 +4360,7 @@
         <v>800</v>
       </c>
       <c r="G59" s="3">
-        <v>700</v>
+        <v>800</v>
       </c>
       <c r="H59" s="3">
         <v>700</v>
@@ -4245,7 +4381,7 @@
         <v>700</v>
       </c>
       <c r="N59" s="3">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="O59" s="3">
         <v>600</v>
@@ -4260,7 +4396,7 @@
         <v>600</v>
       </c>
       <c r="S59" s="3">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="T59" s="3">
         <v>400</v>
@@ -4275,19 +4411,22 @@
         <v>400</v>
       </c>
       <c r="X59" s="3">
+        <v>400</v>
+      </c>
+      <c r="Y59" s="3">
         <v>300</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>200</v>
-      </c>
-      <c r="Z59" s="3">
-        <v>100</v>
       </c>
       <c r="AA59" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB59" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -4304,7 +4443,7 @@
         <v>800</v>
       </c>
       <c r="H60" s="3">
-        <v>700</v>
+        <v>800</v>
       </c>
       <c r="I60" s="3">
         <v>700</v>
@@ -4325,7 +4464,7 @@
         <v>700</v>
       </c>
       <c r="O60" s="3">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="P60" s="3">
         <v>600</v>
@@ -4340,7 +4479,7 @@
         <v>600</v>
       </c>
       <c r="T60" s="3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="U60" s="3">
         <v>500</v>
@@ -4352,19 +4491,22 @@
         <v>500</v>
       </c>
       <c r="X60" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="Y60" s="3">
         <v>400</v>
       </c>
       <c r="Z60" s="3">
+        <v>400</v>
+      </c>
+      <c r="AA60" s="3">
         <v>300</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -4440,8 +4582,11 @@
       <c r="AA61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4517,8 +4662,11 @@
       <c r="AA62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4594,8 +4742,11 @@
       <c r="AA63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4671,8 +4822,11 @@
       <c r="AA64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4748,8 +4902,11 @@
       <c r="AA65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
@@ -4766,7 +4923,7 @@
         <v>800</v>
       </c>
       <c r="H66" s="3">
-        <v>700</v>
+        <v>800</v>
       </c>
       <c r="I66" s="3">
         <v>700</v>
@@ -4787,7 +4944,7 @@
         <v>700</v>
       </c>
       <c r="O66" s="3">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="P66" s="3">
         <v>600</v>
@@ -4802,7 +4959,7 @@
         <v>600</v>
       </c>
       <c r="T66" s="3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="U66" s="3">
         <v>500</v>
@@ -4814,19 +4971,22 @@
         <v>500</v>
       </c>
       <c r="X66" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="Y66" s="3">
         <v>400</v>
       </c>
       <c r="Z66" s="3">
+        <v>400</v>
+      </c>
+      <c r="AA66" s="3">
         <v>300</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4854,8 +5014,9 @@
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
-    </row>
-    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB67" s="3"/>
+    </row>
+    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4931,8 +5092,11 @@
       <c r="AA68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5008,8 +5172,11 @@
       <c r="AA69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5085,8 +5252,11 @@
       <c r="AA70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5162,8 +5332,11 @@
       <c r="AA71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
@@ -5174,7 +5347,7 @@
         <v>-1600</v>
       </c>
       <c r="F72" s="3">
-        <v>-1500</v>
+        <v>-1600</v>
       </c>
       <c r="G72" s="3">
         <v>-1500</v>
@@ -5192,7 +5365,7 @@
         <v>-1500</v>
       </c>
       <c r="L72" s="3">
-        <v>-1400</v>
+        <v>-1500</v>
       </c>
       <c r="M72" s="3">
         <v>-1400</v>
@@ -5210,7 +5383,7 @@
         <v>-1400</v>
       </c>
       <c r="R72" s="3">
-        <v>-1300</v>
+        <v>-1400</v>
       </c>
       <c r="S72" s="3">
         <v>-1300</v>
@@ -5225,22 +5398,25 @@
         <v>-1300</v>
       </c>
       <c r="W72" s="3">
-        <v>-1200</v>
+        <v>-1300</v>
       </c>
       <c r="X72" s="3">
         <v>-1200</v>
       </c>
       <c r="Y72" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="Z72" s="3">
         <v>-1100</v>
-      </c>
-      <c r="Z72" s="3">
-        <v>-1000</v>
       </c>
       <c r="AA72" s="3">
         <v>-1000</v>
       </c>
-    </row>
-    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB72" s="3">
+        <v>-1000</v>
+      </c>
+    </row>
+    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5316,8 +5492,11 @@
       <c r="AA73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5393,8 +5572,11 @@
       <c r="AA74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5470,8 +5652,11 @@
       <c r="AA75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
@@ -5488,7 +5673,7 @@
         <v>-800</v>
       </c>
       <c r="H76" s="3">
-        <v>-700</v>
+        <v>-800</v>
       </c>
       <c r="I76" s="3">
         <v>-700</v>
@@ -5509,7 +5694,7 @@
         <v>-700</v>
       </c>
       <c r="O76" s="3">
-        <v>-600</v>
+        <v>-700</v>
       </c>
       <c r="P76" s="3">
         <v>-600</v>
@@ -5524,7 +5709,7 @@
         <v>-600</v>
       </c>
       <c r="T76" s="3">
-        <v>-500</v>
+        <v>-600</v>
       </c>
       <c r="U76" s="3">
         <v>-500</v>
@@ -5536,19 +5721,22 @@
         <v>-500</v>
       </c>
       <c r="X76" s="3">
-        <v>-400</v>
+        <v>-500</v>
       </c>
       <c r="Y76" s="3">
         <v>-400</v>
       </c>
       <c r="Z76" s="3">
+        <v>-400</v>
+      </c>
+      <c r="AA76" s="3">
         <v>-300</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5624,90 +5812,96 @@
       <c r="AA77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43738</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43555</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43465</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43373</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43281</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43190</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -5772,7 +5966,7 @@
         <v>0</v>
       </c>
       <c r="X81" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="Y81" s="3">
         <v>-100</v>
@@ -5783,8 +5977,11 @@
       <c r="AA81" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB81" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5812,8 +6009,9 @@
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
-    </row>
-    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB82" s="3"/>
+    </row>
+    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5889,8 +6087,11 @@
       <c r="AA83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5966,8 +6167,11 @@
       <c r="AA84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6043,8 +6247,11 @@
       <c r="AA85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6120,8 +6327,11 @@
       <c r="AA86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6197,8 +6407,11 @@
       <c r="AA87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6274,8 +6487,11 @@
       <c r="AA88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -6340,7 +6556,7 @@
         <v>0</v>
       </c>
       <c r="X89" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="Y89" s="3">
         <v>-100</v>
@@ -6349,10 +6565,13 @@
         <v>-100</v>
       </c>
       <c r="AA89" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
+        <v>-100</v>
+      </c>
+      <c r="AB89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6380,8 +6599,9 @@
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
-    </row>
-    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB90" s="3"/>
+    </row>
+    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -6457,8 +6677,11 @@
       <c r="AA91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6534,8 +6757,11 @@
       <c r="AA92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6611,8 +6837,11 @@
       <c r="AA93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -6688,8 +6917,11 @@
       <c r="AA94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6717,8 +6949,9 @@
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
-    </row>
-    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB95" s="3"/>
+    </row>
+    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6794,8 +7027,11 @@
       <c r="AA96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6871,8 +7107,11 @@
       <c r="AA97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6948,8 +7187,11 @@
       <c r="AA98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7025,8 +7267,11 @@
       <c r="AA99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -7091,7 +7336,7 @@
         <v>0</v>
       </c>
       <c r="X100" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Y100" s="3">
         <v>100</v>
@@ -7100,10 +7345,13 @@
         <v>100</v>
       </c>
       <c r="AA100" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="AB100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7179,8 +7427,11 @@
       <c r="AA101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -7254,6 +7505,9 @@
         <v>0</v>
       </c>
       <c r="AA102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/XITO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/XITO_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="92">
   <si>
     <t>XITO</t>
   </si>
@@ -656,125 +656,133 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AB102"/>
+  <dimension ref="A5:AD102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43738</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43646</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43555</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43465</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43373</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43281</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43190</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -853,8 +861,14 @@
       <c r="AB8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC8" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -933,8 +947,14 @@
       <c r="AB9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1013,8 +1033,14 @@
       <c r="AB10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1043,8 +1069,10 @@
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
-    </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC11" s="3"/>
+      <c r="AD11" s="3"/>
+    </row>
+    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1123,8 +1151,14 @@
       <c r="AB12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1203,8 +1237,14 @@
       <c r="AB13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1283,8 +1323,14 @@
       <c r="AB14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1363,8 +1409,14 @@
       <c r="AB15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1390,8 +1442,10 @@
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
-    </row>
-    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC16" s="3"/>
+      <c r="AD16" s="3"/>
+    </row>
+    <row r="17" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1459,19 +1513,25 @@
         <v>0</v>
       </c>
       <c r="Y17" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Z17" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AA17" s="3">
         <v>100</v>
       </c>
       <c r="AB17" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="AC17" s="3">
+        <v>100</v>
+      </c>
+      <c r="AD17" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1539,19 +1599,25 @@
         <v>0</v>
       </c>
       <c r="Y18" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="Z18" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AA18" s="3">
         <v>-100</v>
       </c>
       <c r="AB18" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
+        <v>-100</v>
+      </c>
+      <c r="AC18" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AD18" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1580,8 +1646,10 @@
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
-    </row>
-    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC19" s="3"/>
+      <c r="AD19" s="3"/>
+    </row>
+    <row r="20" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1660,8 +1728,14 @@
       <c r="AB20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1740,8 +1814,14 @@
       <c r="AB21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1772,32 +1852,32 @@
       <c r="L22" s="3">
         <v>0</v>
       </c>
-      <c r="M22" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N22" s="3" t="s">
-        <v>4</v>
+      <c r="M22" s="3">
+        <v>0</v>
+      </c>
+      <c r="N22" s="3">
+        <v>0</v>
       </c>
       <c r="O22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P22" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q22" s="3">
-        <v>0</v>
+      <c r="P22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R22" s="3">
         <v>0</v>
       </c>
-      <c r="S22" s="3" t="s">
-        <v>4</v>
+      <c r="S22" s="3">
+        <v>0</v>
       </c>
       <c r="T22" s="3">
         <v>0</v>
       </c>
-      <c r="U22" s="3">
-        <v>0</v>
+      <c r="U22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V22" s="3">
         <v>0</v>
@@ -1820,8 +1900,14 @@
       <c r="AB22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1889,10 +1975,10 @@
         <v>0</v>
       </c>
       <c r="Y23" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="Z23" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AA23" s="3">
         <v>-100</v>
@@ -1900,8 +1986,14 @@
       <c r="AB23" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC23" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AD23" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="24" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1974,14 +2066,20 @@
       <c r="Z24" s="3">
         <v>0</v>
       </c>
-      <c r="AA24" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AB24" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AA24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2060,8 +2158,14 @@
       <c r="AB25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -2129,10 +2233,10 @@
         <v>0</v>
       </c>
       <c r="Y26" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="Z26" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AA26" s="3">
         <v>-100</v>
@@ -2140,8 +2244,14 @@
       <c r="AB26" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC26" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AD26" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="27" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -2209,10 +2319,10 @@
         <v>0</v>
       </c>
       <c r="Y27" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="Z27" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AA27" s="3">
         <v>-100</v>
@@ -2220,8 +2330,14 @@
       <c r="AB27" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC27" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AD27" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="28" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2300,8 +2416,14 @@
       <c r="AB28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2380,8 +2502,14 @@
       <c r="AB29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2460,8 +2588,14 @@
       <c r="AB30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2540,8 +2674,14 @@
       <c r="AB31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2620,8 +2760,14 @@
       <c r="AB32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -2689,10 +2835,10 @@
         <v>0</v>
       </c>
       <c r="Y33" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="Z33" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AA33" s="3">
         <v>-100</v>
@@ -2700,8 +2846,14 @@
       <c r="AB33" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC33" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AD33" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2780,8 +2932,14 @@
       <c r="AB34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -2849,10 +3007,10 @@
         <v>0</v>
       </c>
       <c r="Y35" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="Z35" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AA35" s="3">
         <v>-100</v>
@@ -2860,93 +3018,105 @@
       <c r="AB35" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC35" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AD35" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43738</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43646</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43555</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43465</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43373</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43281</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43190</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2975,8 +3145,10 @@
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
-    </row>
-    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC39" s="3"/>
+      <c r="AD39" s="3"/>
+    </row>
+    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3005,8 +3177,10 @@
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
-    </row>
-    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC40" s="3"/>
+      <c r="AD40" s="3"/>
+    </row>
+    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
@@ -3085,8 +3259,14 @@
       <c r="AB41" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC41" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD41" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3165,8 +3345,14 @@
       <c r="AB42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3245,8 +3431,14 @@
       <c r="AB43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC43" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3325,8 +3517,14 @@
       <c r="AB44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3405,8 +3603,14 @@
       <c r="AB45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -3485,8 +3689,14 @@
       <c r="AB46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC46" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3565,8 +3775,14 @@
       <c r="AB47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -3645,8 +3861,14 @@
       <c r="AB48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC48" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3725,8 +3947,14 @@
       <c r="AB49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC49" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3805,8 +4033,14 @@
       <c r="AB50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3885,8 +4119,14 @@
       <c r="AB51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3965,8 +4205,14 @@
       <c r="AB52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4045,8 +4291,14 @@
       <c r="AB53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
@@ -4125,8 +4377,14 @@
       <c r="AB54" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC54" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD54" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4155,8 +4413,10 @@
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
-    </row>
-    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC55" s="3"/>
+      <c r="AD55" s="3"/>
+    </row>
+    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4185,8 +4445,10 @@
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
-    </row>
-    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC56" s="3"/>
+      <c r="AD56" s="3"/>
+    </row>
+    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -4265,8 +4527,14 @@
       <c r="AB57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC57" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4319,10 +4587,10 @@
         <v>0</v>
       </c>
       <c r="T58" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="U58" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="V58" s="3">
         <v>100</v>
@@ -4345,8 +4613,14 @@
       <c r="AB58" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC58" s="3">
+        <v>100</v>
+      </c>
+      <c r="AD58" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -4363,10 +4637,10 @@
         <v>800</v>
       </c>
       <c r="H59" s="3">
-        <v>700</v>
+        <v>800</v>
       </c>
       <c r="I59" s="3">
-        <v>700</v>
+        <v>800</v>
       </c>
       <c r="J59" s="3">
         <v>700</v>
@@ -4384,10 +4658,10 @@
         <v>700</v>
       </c>
       <c r="O59" s="3">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="P59" s="3">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="Q59" s="3">
         <v>600</v>
@@ -4399,10 +4673,10 @@
         <v>600</v>
       </c>
       <c r="T59" s="3">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="U59" s="3">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="V59" s="3">
         <v>400</v>
@@ -4414,24 +4688,30 @@
         <v>400</v>
       </c>
       <c r="Y59" s="3">
+        <v>400</v>
+      </c>
+      <c r="Z59" s="3">
+        <v>400</v>
+      </c>
+      <c r="AA59" s="3">
         <v>300</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>200</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AC59" s="3">
         <v>100</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AD59" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>800</v>
+        <v>900</v>
       </c>
       <c r="E60" s="3">
         <v>800</v>
@@ -4446,10 +4726,10 @@
         <v>800</v>
       </c>
       <c r="I60" s="3">
-        <v>700</v>
+        <v>800</v>
       </c>
       <c r="J60" s="3">
-        <v>700</v>
+        <v>800</v>
       </c>
       <c r="K60" s="3">
         <v>700</v>
@@ -4467,10 +4747,10 @@
         <v>700</v>
       </c>
       <c r="P60" s="3">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="Q60" s="3">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="R60" s="3">
         <v>600</v>
@@ -4482,10 +4762,10 @@
         <v>600</v>
       </c>
       <c r="U60" s="3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="V60" s="3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="W60" s="3">
         <v>500</v>
@@ -4494,19 +4774,25 @@
         <v>500</v>
       </c>
       <c r="Y60" s="3">
+        <v>500</v>
+      </c>
+      <c r="Z60" s="3">
+        <v>500</v>
+      </c>
+      <c r="AA60" s="3">
         <v>400</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>400</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AC60" s="3">
         <v>300</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AD60" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -4585,8 +4871,14 @@
       <c r="AB61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4665,8 +4957,14 @@
       <c r="AB62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC62" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4745,8 +5043,14 @@
       <c r="AB63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4825,8 +5129,14 @@
       <c r="AB64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4905,13 +5215,19 @@
       <c r="AB65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>800</v>
+        <v>900</v>
       </c>
       <c r="E66" s="3">
         <v>800</v>
@@ -4926,10 +5242,10 @@
         <v>800</v>
       </c>
       <c r="I66" s="3">
-        <v>700</v>
+        <v>800</v>
       </c>
       <c r="J66" s="3">
-        <v>700</v>
+        <v>800</v>
       </c>
       <c r="K66" s="3">
         <v>700</v>
@@ -4947,10 +5263,10 @@
         <v>700</v>
       </c>
       <c r="P66" s="3">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="Q66" s="3">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="R66" s="3">
         <v>600</v>
@@ -4962,10 +5278,10 @@
         <v>600</v>
       </c>
       <c r="U66" s="3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="V66" s="3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="W66" s="3">
         <v>500</v>
@@ -4974,19 +5290,25 @@
         <v>500</v>
       </c>
       <c r="Y66" s="3">
+        <v>500</v>
+      </c>
+      <c r="Z66" s="3">
+        <v>500</v>
+      </c>
+      <c r="AA66" s="3">
         <v>400</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>400</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>300</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5015,8 +5337,10 @@
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
-    </row>
-    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC67" s="3"/>
+      <c r="AD67" s="3"/>
+    </row>
+    <row r="68" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5095,8 +5419,14 @@
       <c r="AB68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5175,8 +5505,14 @@
       <c r="AB69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5255,8 +5591,14 @@
       <c r="AB70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5335,8 +5677,14 @@
       <c r="AB71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
@@ -5350,10 +5698,10 @@
         <v>-1600</v>
       </c>
       <c r="G72" s="3">
-        <v>-1500</v>
+        <v>-1600</v>
       </c>
       <c r="H72" s="3">
-        <v>-1500</v>
+        <v>-1600</v>
       </c>
       <c r="I72" s="3">
         <v>-1500</v>
@@ -5368,10 +5716,10 @@
         <v>-1500</v>
       </c>
       <c r="M72" s="3">
-        <v>-1400</v>
+        <v>-1500</v>
       </c>
       <c r="N72" s="3">
-        <v>-1400</v>
+        <v>-1500</v>
       </c>
       <c r="O72" s="3">
         <v>-1400</v>
@@ -5386,10 +5734,10 @@
         <v>-1400</v>
       </c>
       <c r="S72" s="3">
-        <v>-1300</v>
+        <v>-1400</v>
       </c>
       <c r="T72" s="3">
-        <v>-1300</v>
+        <v>-1400</v>
       </c>
       <c r="U72" s="3">
         <v>-1300</v>
@@ -5401,22 +5749,28 @@
         <v>-1300</v>
       </c>
       <c r="X72" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="Y72" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="Z72" s="3">
         <v>-1200</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>-1200</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>-1100</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>-1000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5495,8 +5849,14 @@
       <c r="AB73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5575,8 +5935,14 @@
       <c r="AB74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5655,13 +6021,19 @@
       <c r="AB75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>-800</v>
+        <v>-900</v>
       </c>
       <c r="E76" s="3">
         <v>-800</v>
@@ -5676,10 +6048,10 @@
         <v>-800</v>
       </c>
       <c r="I76" s="3">
-        <v>-700</v>
+        <v>-800</v>
       </c>
       <c r="J76" s="3">
-        <v>-700</v>
+        <v>-800</v>
       </c>
       <c r="K76" s="3">
         <v>-700</v>
@@ -5697,10 +6069,10 @@
         <v>-700</v>
       </c>
       <c r="P76" s="3">
-        <v>-600</v>
+        <v>-700</v>
       </c>
       <c r="Q76" s="3">
-        <v>-600</v>
+        <v>-700</v>
       </c>
       <c r="R76" s="3">
         <v>-600</v>
@@ -5712,10 +6084,10 @@
         <v>-600</v>
       </c>
       <c r="U76" s="3">
-        <v>-500</v>
+        <v>-600</v>
       </c>
       <c r="V76" s="3">
-        <v>-500</v>
+        <v>-600</v>
       </c>
       <c r="W76" s="3">
         <v>-500</v>
@@ -5724,19 +6096,25 @@
         <v>-500</v>
       </c>
       <c r="Y76" s="3">
+        <v>-500</v>
+      </c>
+      <c r="Z76" s="3">
+        <v>-500</v>
+      </c>
+      <c r="AA76" s="3">
         <v>-400</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>-400</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>-300</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5815,93 +6193,105 @@
       <c r="AB77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43738</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43646</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43555</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43465</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43373</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43281</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43190</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -5969,10 +6359,10 @@
         <v>0</v>
       </c>
       <c r="Y81" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="Z81" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AA81" s="3">
         <v>-100</v>
@@ -5980,8 +6370,14 @@
       <c r="AB81" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC81" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AD81" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6010,8 +6406,10 @@
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
-    </row>
-    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC82" s="3"/>
+      <c r="AD82" s="3"/>
+    </row>
+    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6090,8 +6488,14 @@
       <c r="AB83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6170,8 +6574,14 @@
       <c r="AB84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6250,8 +6660,14 @@
       <c r="AB85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6330,8 +6746,14 @@
       <c r="AB86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6410,8 +6832,14 @@
       <c r="AB87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6490,8 +6918,14 @@
       <c r="AB88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -6559,19 +6993,25 @@
         <v>0</v>
       </c>
       <c r="Y89" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="Z89" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AA89" s="3">
         <v>-100</v>
       </c>
       <c r="AB89" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
+        <v>-100</v>
+      </c>
+      <c r="AC89" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AD89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6600,8 +7040,10 @@
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
-    </row>
-    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC90" s="3"/>
+      <c r="AD90" s="3"/>
+    </row>
+    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -6680,8 +7122,14 @@
       <c r="AB91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6760,8 +7208,14 @@
       <c r="AB92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6840,8 +7294,14 @@
       <c r="AB93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -6920,8 +7380,14 @@
       <c r="AB94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6950,8 +7416,10 @@
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
-    </row>
-    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC95" s="3"/>
+      <c r="AD95" s="3"/>
+    </row>
+    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7030,8 +7498,14 @@
       <c r="AB96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7110,8 +7584,14 @@
       <c r="AB97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7190,8 +7670,14 @@
       <c r="AB98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7270,8 +7756,14 @@
       <c r="AB99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -7339,19 +7831,25 @@
         <v>0</v>
       </c>
       <c r="Y100" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Z100" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AA100" s="3">
         <v>100</v>
       </c>
       <c r="AB100" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="AC100" s="3">
+        <v>100</v>
+      </c>
+      <c r="AD100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7430,8 +7928,14 @@
       <c r="AB101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -7508,6 +8012,12 @@
         <v>0</v>
       </c>
       <c r="AB102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD102" s="3">
         <v>0</v>
       </c>
     </row>
